--- a/samples/收支流水.xlsx
+++ b/samples/收支流水.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="八月" sheetId="1" r:id="rId1"/>
+    <sheet name="九月" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -564,4 +565,95 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>日期</v>
+      </c>
+      <c r="B1" t="str">
+        <v>项目</v>
+      </c>
+      <c r="C1" t="str">
+        <v>类别</v>
+      </c>
+      <c r="D1" t="str">
+        <v>金额</v>
+      </c>
+      <c r="E1" t="str">
+        <v>收支</v>
+      </c>
+      <c r="F1" t="str">
+        <v>备注</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="B2" t="str">
+        <v>域名续费</v>
+      </c>
+      <c r="C2" t="str">
+        <v>办公</v>
+      </c>
+      <c r="D2">
+        <v>68</v>
+      </c>
+      <c r="E2" t="str">
+        <v>支出</v>
+      </c>
+      <c r="F2" t="str">
+        <v>collecout.cn</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09-06</v>
+      </c>
+      <c r="B3" t="str">
+        <v>外包测试</v>
+      </c>
+      <c r="C3" t="str">
+        <v>支出</v>
+      </c>
+      <c r="D3">
+        <v>800</v>
+      </c>
+      <c r="E3" t="str">
+        <v>支出</v>
+      </c>
+      <c r="F3" t="str">
+        <v>安卓兼容性回归</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B4" t="str">
+        <v>授权费</v>
+      </c>
+      <c r="C4" t="str">
+        <v>收入</v>
+      </c>
+      <c r="D4">
+        <v>2400</v>
+      </c>
+      <c r="E4" t="str">
+        <v>收入</v>
+      </c>
+      <c r="F4" t="str">
+        <v>第二个内测用户</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
 </file>